--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,56 +417,56 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>收益率%</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>年化收益率%</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>最大回撤%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>年化波动率%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>夏普比率</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>策略</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>314.0288196868395</v>
+        <v>314.0288196868393</v>
       </c>
       <c r="C2" t="n">
-        <v>21.13907554916148</v>
+        <v>21.13907554916146</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016688</v>
+        <v>37.5595354501669</v>
       </c>
       <c r="E2" t="n">
-        <v>25.26420793571159</v>
+        <v>25.26420793571156</v>
       </c>
       <c r="F2" t="n">
         <v>0.7377660758885173</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>沪深300</t>
         </is>
@@ -500,7 +488,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>中证500</t>
         </is>
@@ -515,10 +503,10 @@
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.15747636530747</v>
+        <v>22.15747636530745</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1841580342136148</v>
+        <v>0.1841580342136149</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>314.0288196868393</v>
+        <v>314.0288196868394</v>
       </c>
       <c r="C2" t="n">
         <v>21.13907554916146</v>
       </c>
       <c r="D2" t="n">
-        <v>37.5595354501669</v>
+        <v>37.55953545016687</v>
       </c>
       <c r="E2" t="n">
-        <v>25.26420793571156</v>
+        <v>25.26420793571157</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7377660758885173</v>
+        <v>0.7377660758885172</v>
       </c>
     </row>
     <row r="3">

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>314.0288196868394</v>
+        <v>313.7055045394395</v>
       </c>
       <c r="C2" t="n">
-        <v>21.13907554916146</v>
+        <v>21.1138754852479</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016687</v>
+        <v>37.55953545016688</v>
       </c>
       <c r="E2" t="n">
-        <v>25.26420793571157</v>
+        <v>25.25751549253335</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7377660758885172</v>
+        <v>0.7369638352097835</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.00673698470585</v>
+        <v>37.07772071992041</v>
       </c>
       <c r="C3" t="n">
-        <v>4.341449055377544</v>
+        <v>4.346366283921066</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.30480894674027</v>
+        <v>19.29964089880752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09538810047060756</v>
+        <v>0.09566842686876874</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60.34533159663167</v>
+        <v>59.28192798037437</v>
       </c>
       <c r="C4" t="n">
-        <v>6.580477290569653</v>
+        <v>6.481214830749638</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.15747636530745</v>
+        <v>22.15302614562329</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1841580342136149</v>
+        <v>0.1797142658785782</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>313.7055045394395</v>
+        <v>310.5752491575395</v>
       </c>
       <c r="C2" t="n">
-        <v>21.1138754852479</v>
+        <v>20.97751028380319</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016688</v>
+        <v>37.55953545016686</v>
       </c>
       <c r="E2" t="n">
-        <v>25.25751549253335</v>
+        <v>25.25266221859631</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7369638352097835</v>
+        <v>0.7317054385733703</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.07772071992041</v>
+        <v>36.07653931065777</v>
       </c>
       <c r="C3" t="n">
-        <v>4.346366283921066</v>
+        <v>4.240909466520026</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.29964089880752</v>
+        <v>19.29646410565169</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09566842686876874</v>
+        <v>0.09021909179776287</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59.28192798037437</v>
+        <v>55.99076325976525</v>
       </c>
       <c r="C4" t="n">
-        <v>6.481214830749638</v>
+        <v>6.178308997610116</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.15302614562329</v>
+        <v>22.16052760251243</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1797142658785782</v>
+        <v>0.1659847212840316</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>310.5752491575395</v>
+        <v>298.2721161051395</v>
       </c>
       <c r="C2" t="n">
-        <v>20.97751028380319</v>
+        <v>20.47026298279373</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016686</v>
+        <v>37.5595354501669</v>
       </c>
       <c r="E2" t="n">
-        <v>25.25266221859631</v>
+        <v>25.27129207831566</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7317054385733703</v>
+        <v>0.7110939530556625</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.07653931065777</v>
+        <v>36.68960920300819</v>
       </c>
       <c r="C3" t="n">
-        <v>4.240909466520026</v>
+        <v>4.301758151620705</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.29646410565169</v>
+        <v>19.29193697626921</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09021909179776287</v>
+        <v>0.09339436230986173</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55.99076325976525</v>
+        <v>57.55536340455441</v>
       </c>
       <c r="C4" t="n">
-        <v>6.178308997610116</v>
+        <v>6.31779728599573</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.16052760251243</v>
+        <v>22.15745654987902</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1659847212840316</v>
+        <v>0.1723030473918079</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>298.2721161051395</v>
+        <v>307.7183390112396</v>
       </c>
       <c r="C2" t="n">
-        <v>20.47026298279373</v>
+        <v>20.83918672957095</v>
       </c>
       <c r="D2" t="n">
-        <v>37.5595354501669</v>
+        <v>37.55953545016686</v>
       </c>
       <c r="E2" t="n">
-        <v>25.27129207831566</v>
+        <v>25.27844906798958</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7110939530556625</v>
+        <v>0.7254870217807031</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.68960920300819</v>
+        <v>34.48649601266269</v>
       </c>
       <c r="C3" t="n">
-        <v>4.301758151620705</v>
+        <v>4.071397876812943</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.29193697626921</v>
+        <v>19.29611973543226</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09339436230986173</v>
+        <v>0.08143595180576554</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57.55536340455441</v>
+        <v>53.28708398755786</v>
       </c>
       <c r="C4" t="n">
-        <v>6.31779728599573</v>
+        <v>5.921774895257803</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.15745654987902</v>
+        <v>22.17439597329484</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1723030473918079</v>
+        <v>0.1543119776240457</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>307.7183390112396</v>
+        <v>299.0188045125393</v>
       </c>
       <c r="C2" t="n">
-        <v>20.83918672957095</v>
+        <v>20.47666936014048</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016686</v>
+        <v>37.55953545016688</v>
       </c>
       <c r="E2" t="n">
-        <v>25.27844906798958</v>
+        <v>25.28483472919062</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7254870217807031</v>
+        <v>0.7109664568772888</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.48649601266269</v>
+        <v>34.01016466195994</v>
       </c>
       <c r="C3" t="n">
-        <v>4.071397876812943</v>
+        <v>4.019484191803646</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.29611973543226</v>
+        <v>19.29145939235539</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08143595180576554</v>
+        <v>0.07876460566823529</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.28708398755786</v>
+        <v>51.00923903649883</v>
       </c>
       <c r="C4" t="n">
-        <v>5.921774895257803</v>
+        <v>5.705267008163761</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.17439597329484</v>
+        <v>22.17547022357403</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1543119776240457</v>
+        <v>0.1445411067205396</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>299.0188045125393</v>
+        <v>289.9938271906395</v>
       </c>
       <c r="C2" t="n">
-        <v>20.47666936014048</v>
+        <v>20.09446280280989</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016688</v>
+        <v>37.55953545016689</v>
       </c>
       <c r="E2" t="n">
-        <v>25.28483472919062</v>
+        <v>25.29275444353665</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7109664568772888</v>
+        <v>0.695632531525486</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.01016466195994</v>
+        <v>29.63744215827606</v>
       </c>
       <c r="C3" t="n">
-        <v>4.019484191803646</v>
+        <v>3.554064883819619</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.29145939235539</v>
+        <v>19.32393279672632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07876460566823529</v>
+        <v>0.05454712013892889</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51.00923903649883</v>
+        <v>44.79587246987271</v>
       </c>
       <c r="C4" t="n">
-        <v>5.705267008163761</v>
+        <v>5.106288713748164</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.17547022357403</v>
+        <v>22.22165387838745</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1445411067205396</v>
+        <v>0.1172859917633319</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>289.9938271906395</v>
+        <v>269.1481394325394</v>
       </c>
       <c r="C2" t="n">
-        <v>20.09446280280989</v>
+        <v>19.19895569316448</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016689</v>
+        <v>37.5595354501669</v>
       </c>
       <c r="E2" t="n">
-        <v>25.29275444353665</v>
+        <v>25.36429858452597</v>
       </c>
       <c r="F2" t="n">
-        <v>0.695632531525486</v>
+        <v>0.6583645763952658</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29.63744215827606</v>
+        <v>31.30193460388244</v>
       </c>
       <c r="C3" t="n">
-        <v>3.554064883819619</v>
+        <v>3.729938737464322</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.32393279672632</v>
+        <v>19.32432174778029</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05454712013892889</v>
+        <v>0.06364718790741519</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.79587246987271</v>
+        <v>47.84383367375784</v>
       </c>
       <c r="C4" t="n">
-        <v>5.106288713748164</v>
+        <v>5.398330114079797</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.22165387838745</v>
+        <v>22.22875344439965</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1172859917633319</v>
+        <v>0.1303865338796138</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>269.1481394325394</v>
+        <v>285.0396154837395</v>
       </c>
       <c r="C2" t="n">
-        <v>19.19895569316448</v>
+        <v>19.8648725019221</v>
       </c>
       <c r="D2" t="n">
-        <v>37.5595354501669</v>
+        <v>37.55953545016688</v>
       </c>
       <c r="E2" t="n">
-        <v>25.36429858452597</v>
+        <v>25.40473256207668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6583645763952658</v>
+        <v>0.683529041665402</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.30193460388244</v>
+        <v>33.1430104979398</v>
       </c>
       <c r="C3" t="n">
-        <v>3.729938737464322</v>
+        <v>3.922213695476651</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.32432174778029</v>
+        <v>19.32579046395493</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06364718790741519</v>
+        <v>0.0735914889550966</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.84383367375784</v>
+        <v>51.15769637734837</v>
       </c>
       <c r="C4" t="n">
-        <v>5.398330114079797</v>
+        <v>5.7098429421782</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.22875344439965</v>
+        <v>22.2375963432587</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1303865338796138</v>
+        <v>0.1443430707452004</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>285.0396154837395</v>
+        <v>292.8297879544396</v>
       </c>
       <c r="C2" t="n">
-        <v>19.8648725019221</v>
+        <v>20.1762099005899</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016688</v>
+        <v>37.5595354501669</v>
       </c>
       <c r="E2" t="n">
-        <v>25.40473256207668</v>
+        <v>25.40789133282853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.683529041665402</v>
+        <v>0.6956976346065828</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.1430104979398</v>
+        <v>31.38444428312259</v>
       </c>
       <c r="C3" t="n">
-        <v>3.922213695476651</v>
+        <v>3.73464235564005</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.32579046395493</v>
+        <v>19.32690981257383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0735914889550966</v>
+        <v>0.06388203637380289</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51.15769637734837</v>
+        <v>48.71479871516667</v>
       </c>
       <c r="C4" t="n">
-        <v>5.7098429421782</v>
+        <v>5.475612264880847</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.2375963432587</v>
+        <v>22.23986898695685</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1443430707452004</v>
+        <v>0.1337963036844314</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>292.8297879544396</v>
+        <v>294.7703506624394</v>
       </c>
       <c r="C2" t="n">
-        <v>20.1762099005899</v>
+        <v>20.24396918445879</v>
       </c>
       <c r="D2" t="n">
-        <v>37.5595354501669</v>
+        <v>37.55953545016688</v>
       </c>
       <c r="E2" t="n">
-        <v>25.40789133282853</v>
+        <v>25.40155881902071</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6956976346065828</v>
+        <v>0.6985385940634513</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.38444428312259</v>
+        <v>32.11906182806248</v>
       </c>
       <c r="C3" t="n">
-        <v>3.73464235564005</v>
+        <v>3.810297949902663</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.32690981257383</v>
+        <v>19.32276050470718</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06388203637380289</v>
+        <v>0.06781111578666331</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.71479871516667</v>
+        <v>50.57290806581329</v>
       </c>
       <c r="C4" t="n">
-        <v>5.475612264880847</v>
+        <v>5.648593682527236</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.23986898695685</v>
+        <v>22.23842264930285</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1337963036844314</v>
+        <v>0.1415834986221894</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>294.7703506624394</v>
+        <v>303.7137920420395</v>
       </c>
       <c r="C2" t="n">
-        <v>20.24396918445879</v>
+        <v>20.59412983432491</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016688</v>
+        <v>37.55953545016687</v>
       </c>
       <c r="E2" t="n">
-        <v>25.40155881902071</v>
+        <v>25.40733719943981</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6985385940634513</v>
+        <v>0.7121615969549089</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.11906182806248</v>
+        <v>31.80744466827927</v>
       </c>
       <c r="C3" t="n">
-        <v>3.810297949902663</v>
+        <v>3.775342959459449</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.32276050470718</v>
+        <v>19.31784395845305</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06781111578666331</v>
+        <v>0.06601890781405696</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.57290806581329</v>
+        <v>50.88638698200641</v>
       </c>
       <c r="C4" t="n">
-        <v>5.648593682527236</v>
+        <v>5.674989278224252</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.23842264930285</v>
+        <v>22.23259199734398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1415834986221894</v>
+        <v>0.1428078776691243</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>303.7137920420395</v>
+        <v>304.4364635670394</v>
       </c>
       <c r="C2" t="n">
-        <v>20.59412983432491</v>
+        <v>20.6110380209821</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016687</v>
+        <v>37.55953545016688</v>
       </c>
       <c r="E2" t="n">
-        <v>25.40733719943981</v>
+        <v>25.40059406542409</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7121615969549089</v>
+        <v>0.7130163166394319</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.80744466827927</v>
+        <v>30.57795097471363</v>
       </c>
       <c r="C3" t="n">
-        <v>3.775342959459449</v>
+        <v>3.642947713517852</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.31784395845305</v>
+        <v>19.31586591990634</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06601890781405696</v>
+        <v>0.05917144580818225</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.88638698200641</v>
+        <v>48.23211629929646</v>
       </c>
       <c r="C4" t="n">
-        <v>5.674989278224252</v>
+        <v>5.42066175956426</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.23259199734398</v>
+        <v>22.23634573135008</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1428078776691243</v>
+        <v>0.1313463009997431</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>304.4364635670394</v>
+        <v>300.0332276594394</v>
       </c>
       <c r="C2" t="n">
-        <v>20.6110380209821</v>
+        <v>20.42218250337777</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016688</v>
+        <v>37.55953545016691</v>
       </c>
       <c r="E2" t="n">
-        <v>25.40059406542409</v>
+        <v>25.39748399358201</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7130163166394319</v>
+        <v>0.7056676365228438</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.57795097471363</v>
+        <v>32.80853511413435</v>
       </c>
       <c r="C3" t="n">
-        <v>3.642947713517852</v>
+        <v>3.876552068913863</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.31586591990634</v>
+        <v>19.32059593138851</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05917144580818225</v>
+        <v>0.07124790942278841</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.23211629929646</v>
+        <v>50.81572822325684</v>
       </c>
       <c r="C4" t="n">
-        <v>5.42066175956426</v>
+        <v>5.662149809257033</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.23634573135008</v>
+        <v>22.23926420627875</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1313463009997431</v>
+        <v>0.1421876991939451</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>300.0332276594394</v>
+        <v>309.4967305723732</v>
       </c>
       <c r="C2" t="n">
-        <v>20.42218250337777</v>
+        <v>20.78805337535072</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016691</v>
+        <v>37.55953545016688</v>
       </c>
       <c r="E2" t="n">
-        <v>25.39748399358201</v>
+        <v>25.40442735368341</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7056676365228438</v>
+        <v>0.7198766231075516</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.80853511413435</v>
+        <v>31.42493180238557</v>
       </c>
       <c r="C3" t="n">
-        <v>3.876552068913863</v>
+        <v>3.72881412392787</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.32059593138851</v>
+        <v>19.31938473681047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07124790942278841</v>
+        <v>0.06360524109168608</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.81572822325684</v>
+        <v>47.99795578042183</v>
       </c>
       <c r="C4" t="n">
-        <v>5.662149809257033</v>
+        <v>5.392420366447648</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.23926420627875</v>
+        <v>22.24422296211042</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1421876991939451</v>
+        <v>0.1300301822803357</v>
       </c>
     </row>
   </sheetData>

--- a/data/策略表现指标.xlsx
+++ b/data/策略表现指标.xlsx
@@ -450,19 +450,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>309.4967305723732</v>
+        <v>304.1264777665731</v>
       </c>
       <c r="C2" t="n">
-        <v>20.78805337535072</v>
+        <v>20.56263511073826</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55953545016688</v>
+        <v>37.5595354501669</v>
       </c>
       <c r="E2" t="n">
-        <v>25.40442735368341</v>
+        <v>25.4028345422188</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7198766231075516</v>
+        <v>0.7110480163431631</v>
       </c>
     </row>
     <row r="3">
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.42493180238557</v>
+        <v>30.30622273628574</v>
       </c>
       <c r="C3" t="n">
-        <v>3.72881412392787</v>
+        <v>3.608132693787724</v>
       </c>
       <c r="D3" t="n">
         <v>45.60262048486479</v>
       </c>
       <c r="E3" t="n">
-        <v>19.31938473681047</v>
+        <v>19.31689120187879</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06360524109168608</v>
+        <v>0.05736599550138511</v>
       </c>
     </row>
     <row r="4">
@@ -494,19 +494,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.99795578042183</v>
+        <v>46.62885330078006</v>
       </c>
       <c r="C4" t="n">
-        <v>5.392420366447648</v>
+        <v>5.258408794237623</v>
       </c>
       <c r="D4" t="n">
         <v>41.80801038538575</v>
       </c>
       <c r="E4" t="n">
-        <v>22.24422296211042</v>
+        <v>22.24105924399131</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1300301822803357</v>
+        <v>0.1240232654379013</v>
       </c>
     </row>
   </sheetData>
